--- a/artfynd/A 16890-2024 artfynd.xlsx
+++ b/artfynd/A 16890-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88176477</v>
+        <v>88176475</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444599.6749167092</v>
+        <v>444600</v>
       </c>
       <c r="R2" t="n">
-        <v>6928965.150940636</v>
+        <v>6928965</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -751,19 +746,9 @@
           <t>2020-09-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,57 +776,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88176479</v>
+        <v>89596101</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vemdalsskalet, Hjd</t>
+          <t>Strömsfjällvallen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444599.6749167092</v>
+        <v>444616</v>
       </c>
       <c r="R3" t="n">
-        <v>6928965.150940636</v>
+        <v>6928914</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,96 +844,81 @@
           <t>2020-09-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-25</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>Jan Henriksson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88176475</v>
+        <v>119383162</v>
       </c>
       <c r="B4" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vemdalsskalet, Hjd</t>
+          <t>Högarhålen, Högarhålen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444599.6749167092</v>
+        <v>444630</v>
       </c>
       <c r="R4" t="n">
-        <v>6928965.150940636</v>
+        <v>6928858</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,22 +942,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,72 +966,66 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89596103</v>
+        <v>119382032</v>
       </c>
       <c r="B5" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>4412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Strömsfjällvallen, Hjd</t>
+          <t>Skalsbäcken, Skalsbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444618.1258910247</v>
+        <v>444594</v>
       </c>
       <c r="R5" t="n">
-        <v>6928905.194770865</v>
+        <v>6928930</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,22 +1049,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,53 +1079,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89596099</v>
+        <v>89596104</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1180,10 +1126,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444584.7789950526</v>
+        <v>444605</v>
       </c>
       <c r="R6" t="n">
-        <v>6928904.82489795</v>
+        <v>6928896</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,19 +1159,9 @@
           <t>2020-09-25</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,53 +1192,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89596100</v>
+        <v>119382772</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Strömsfjällvallen, Hjd</t>
+          <t>Skalsbäcken, Skalsbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444610.1237507955</v>
+        <v>444620</v>
       </c>
       <c r="R7" t="n">
-        <v>6928925.211077331</v>
+        <v>6928943</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1326,22 +1257,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,69 +1287,63 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89596098</v>
+        <v>88176477</v>
       </c>
       <c r="B8" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Strömsfjällvallen, Hjd</t>
+          <t>Vemdalsskalet, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444582.9900288882</v>
+        <v>444600</v>
       </c>
       <c r="R8" t="n">
-        <v>6928880.809742031</v>
+        <v>6928965</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1445,34 +1370,25 @@
           <t>2020-09-25</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-09-25</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -1480,23 +1396,14 @@
           <t>Jan Henriksson</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89596101</v>
+        <v>89596099</v>
       </c>
       <c r="B9" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,21 +1411,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1528,10 +1435,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444615.9573267199</v>
+        <v>444585</v>
       </c>
       <c r="R9" t="n">
-        <v>6928914.016450136</v>
+        <v>6928905</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,19 +1468,9 @@
           <t>2020-09-25</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,15 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89596104</v>
+        <v>89596102</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1620,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1644,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444605.0097939175</v>
+        <v>444620</v>
       </c>
       <c r="R10" t="n">
-        <v>6928896.164969346</v>
+        <v>6928906</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,19 +1569,9 @@
           <t>2020-09-25</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,37 +1602,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89596102</v>
+        <v>89596103</v>
       </c>
       <c r="B11" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1760,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444619.9930217727</v>
+        <v>444618</v>
       </c>
       <c r="R11" t="n">
-        <v>6928906.088510934</v>
+        <v>6928905</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,19 +1670,9 @@
           <t>2020-09-25</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1836,53 +1703,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119382032</v>
+        <v>89596098</v>
       </c>
       <c r="B12" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4412</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skalsbäcken, Skalsbäcken, Hjd</t>
+          <t>Strömsfjällvallen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444594</v>
+        <v>444583</v>
       </c>
       <c r="R12" t="n">
-        <v>6928930</v>
+        <v>6928881</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1906,22 +1768,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:35</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:35</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,65 +1788,68 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119383162</v>
+        <v>88176479</v>
       </c>
       <c r="B13" t="n">
-        <v>90576</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Högarhålen, Högarhålen, Hjd</t>
+          <t>Vemdalsskalet, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444630</v>
+        <v>444600</v>
       </c>
       <c r="R13" t="n">
-        <v>6928858</v>
+        <v>6928965</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2018,22 +1873,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:51</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:51</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,66 +1887,67 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119383113</v>
+        <v>89596100</v>
       </c>
       <c r="B14" t="n">
-        <v>90954</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Högarhålen, Högarhålen, Hjd</t>
+          <t>Strömsfjällvallen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444631</v>
+        <v>444610</v>
       </c>
       <c r="R14" t="n">
-        <v>6928873</v>
+        <v>6928925</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2125,22 +1971,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:45</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:45</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2155,49 +1991,48 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119382772</v>
+        <v>119381849</v>
       </c>
       <c r="B15" t="n">
-        <v>74638</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2207,10 +2042,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444620</v>
+        <v>444622</v>
       </c>
       <c r="R15" t="n">
-        <v>6928943</v>
+        <v>6928886</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2242,7 +2077,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2252,7 +2087,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2279,50 +2114,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119381849</v>
+        <v>119383113</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92329</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6040186</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skalsbäcken, Skalsbäcken, Hjd</t>
+          <t>Högarhålen, Högarhålen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444622</v>
+        <v>444631</v>
       </c>
       <c r="R16" t="n">
-        <v>6928886</v>
+        <v>6928873</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2354,7 +2184,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2364,7 +2194,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 16890-2024 artfynd.xlsx
+++ b/artfynd/A 16890-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88176475</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596101</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119383162</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119382032</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596104</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119382772</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1397,6 +1432,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88176477</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596099</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1599,6 +1644,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596102</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1700,6 +1750,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596103</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1799,6 +1854,11 @@
       <c r="AY12" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596098</t>
         </is>
       </c>
     </row>
@@ -1903,6 +1963,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88176479</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2004,6 +2069,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596100</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2111,6 +2181,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119381849</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2218,8 +2293,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119383113</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>